--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260916.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260916.xlsx
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>1,102,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>1,000,000</t>
+          <t>1,102,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>上銀</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1701,12 +1701,12 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>上銀</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
